--- a/public/template/country.xlsx
+++ b/public/template/country.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lara\www\erp6-be-golang\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5044A34-D00C-4EB1-9274-63DE7AE97F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C19641F-C083-4DFB-A958-3193B9C4E8D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="1620" windowWidth="14250" windowHeight="13725" xr2:uid="{10884B7F-BA6B-400C-A1CB-3934E3A296F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{168BEC72-4B80-41B5-8329-2CDC0F7E6CBF}"/>
   </bookViews>
   <sheets>
     <sheet name="country" sheetId="1" r:id="rId1"/>
@@ -20,13 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="448">
-  <si>
-    <t>recordstatus</t>
-  </si>
-  <si>
-    <t>updatedate</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="449">
   <si>
     <t>AD</t>
   </si>
@@ -1360,10 +1354,19 @@
     <t>ZIMBABWE</t>
   </si>
   <si>
+    <t>Country ID</t>
+  </si>
+  <si>
     <t>Country Code</t>
   </si>
   <si>
     <t>Country Name</t>
+  </si>
+  <si>
+    <t>Record Status</t>
+  </si>
+  <si>
+    <t>Update Date</t>
   </si>
 </sst>
 </file>
@@ -2204,28 +2207,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC1CD91-0563-4073-BE36-9C05509B38CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2501896C-0E31-4BAB-BE8B-01FC84C2C4CC}">
   <dimension ref="A1:E223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>184</v>
+        <v>444</v>
       </c>
       <c r="B1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C1" t="s">
         <v>446</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>447</v>
       </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
       <c r="E1" t="s">
-        <v>1</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2233,10 +2240,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2250,10 +2257,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2267,10 +2274,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2284,10 +2291,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2301,10 +2308,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2318,10 +2325,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2335,10 +2342,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2352,10 +2359,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2369,10 +2376,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2386,10 +2393,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2403,10 +2410,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2420,10 +2427,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2437,10 +2444,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2454,10 +2461,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2471,10 +2478,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2488,10 +2495,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2505,10 +2512,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2522,10 +2529,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -2539,10 +2546,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -2556,10 +2563,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -2573,10 +2580,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2590,10 +2597,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2607,10 +2614,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2624,10 +2631,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2641,10 +2648,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2658,10 +2665,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2675,10 +2682,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2692,10 +2699,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2709,10 +2716,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -2726,10 +2733,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2743,10 +2750,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -2760,10 +2767,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2777,10 +2784,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2794,10 +2801,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2811,10 +2818,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2828,10 +2835,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2845,10 +2852,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2862,10 +2869,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2879,10 +2886,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -2896,10 +2903,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2913,10 +2920,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -2930,10 +2937,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2947,10 +2954,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2964,10 +2971,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2981,10 +2988,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2998,10 +3005,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -3015,10 +3022,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3032,10 +3039,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -3049,10 +3056,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -3066,10 +3073,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -3083,10 +3090,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -3100,10 +3107,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C53" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -3117,10 +3124,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C54" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -3134,10 +3141,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C55" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3151,10 +3158,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C56" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3168,10 +3175,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C57" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -3185,10 +3192,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C58" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -3202,10 +3209,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C59" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3219,10 +3226,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C60" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3236,10 +3243,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3253,10 +3260,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3270,10 +3277,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C63" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3287,10 +3294,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C64" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3304,10 +3311,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C65" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3321,10 +3328,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C66" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3338,10 +3345,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C67" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3355,10 +3362,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C68" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3372,10 +3379,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C69" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3389,10 +3396,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C70" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3406,10 +3413,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C71" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3423,10 +3430,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C72" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -3440,10 +3447,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3457,10 +3464,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C74" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3474,10 +3481,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C75" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3491,10 +3498,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C76" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3508,10 +3515,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C77" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3525,10 +3532,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C78" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3542,10 +3549,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C79" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3559,10 +3566,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C80" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3576,10 +3583,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C81" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3593,10 +3600,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C82" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3610,10 +3617,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C83" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3627,10 +3634,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C84" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3644,10 +3651,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C85" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3661,10 +3668,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C86" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3678,10 +3685,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C87" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3695,10 +3702,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C88" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3712,10 +3719,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C89" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3729,10 +3736,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C90" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3746,10 +3753,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C91" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3763,10 +3770,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C92" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3780,10 +3787,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C93" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3797,10 +3804,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C94" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3814,10 +3821,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C95" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3831,10 +3838,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C96" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3848,10 +3855,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C97" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3865,10 +3872,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C98" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3882,10 +3889,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C99" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3899,10 +3906,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C100" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3916,10 +3923,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C101" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3933,10 +3940,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C102" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3950,10 +3957,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C103" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3967,10 +3974,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C104" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3984,10 +3991,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C105" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -4001,10 +4008,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C106" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -4018,10 +4025,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C107" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -4035,10 +4042,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C108" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -4052,10 +4059,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C109" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -4069,10 +4076,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C110" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -4086,10 +4093,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C111" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -4103,10 +4110,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C112" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -4120,10 +4127,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C113" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -4137,10 +4144,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C114" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -4154,10 +4161,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C115" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -4171,10 +4178,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C116" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -4188,10 +4195,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C117" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4205,10 +4212,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C118" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4222,10 +4229,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C119" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4239,10 +4246,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C120" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4256,10 +4263,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C121" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4273,10 +4280,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C122" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -4290,10 +4297,10 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C123" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4307,10 +4314,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C124" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4324,10 +4331,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C125" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4341,10 +4348,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C126" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4358,10 +4365,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C127" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4375,10 +4382,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C128" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4392,10 +4399,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C129" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4409,10 +4416,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C130" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -4426,10 +4433,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C131" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -4443,10 +4450,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C132" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -4460,10 +4467,10 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C133" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -4477,10 +4484,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C134" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -4494,10 +4501,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C135" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4511,10 +4518,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C136" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -4528,10 +4535,10 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C137" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -4545,10 +4552,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C138" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -4562,10 +4569,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C139" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -4579,10 +4586,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C140" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4596,10 +4603,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C141" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4613,10 +4620,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C142" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4630,10 +4637,10 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C143" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -4647,10 +4654,10 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C144" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -4664,10 +4671,10 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C145" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -4681,10 +4688,10 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C146" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -4698,10 +4705,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C147" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -4715,10 +4722,10 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C148" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -4732,10 +4739,10 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C149" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -4749,10 +4756,10 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C150" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -4766,10 +4773,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C151" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -4783,10 +4790,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C152" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -4800,10 +4807,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C153" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -4817,10 +4824,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C154" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D154">
         <v>1</v>
@@ -4834,10 +4841,10 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C155" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -4851,10 +4858,10 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C156" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -4868,10 +4875,10 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C157" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -4885,10 +4892,10 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C158" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -4902,10 +4909,10 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C159" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -4919,10 +4926,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -4936,10 +4943,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C161" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -4953,10 +4960,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C162" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -4970,10 +4977,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C163" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D163">
         <v>1</v>
@@ -4987,10 +4994,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C164" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -5004,10 +5011,10 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C165" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -5021,10 +5028,10 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C166" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -5038,10 +5045,10 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C167" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D167">
         <v>1</v>
@@ -5055,10 +5062,10 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C168" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -5072,10 +5079,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C169" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -5089,10 +5096,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C170" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -5106,10 +5113,10 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C171" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D171">
         <v>1</v>
@@ -5123,10 +5130,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C172" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -5140,10 +5147,10 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C173" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -5157,10 +5164,10 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C174" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -5174,10 +5181,10 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C175" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D175">
         <v>1</v>
@@ -5191,10 +5198,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C176" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -5208,10 +5215,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C177" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D177">
         <v>1</v>
@@ -5225,10 +5232,10 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C178" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -5242,10 +5249,10 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C179" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D179">
         <v>1</v>
@@ -5259,10 +5266,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C180" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D180">
         <v>1</v>
@@ -5276,10 +5283,10 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C181" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -5293,10 +5300,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C182" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D182">
         <v>1</v>
@@ -5310,10 +5317,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C183" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D183">
         <v>1</v>
@@ -5327,10 +5334,10 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C184" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D184">
         <v>1</v>
@@ -5344,10 +5351,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C185" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -5361,10 +5368,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C186" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -5378,10 +5385,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C187" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -5395,10 +5402,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C188" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -5412,10 +5419,10 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C189" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -5429,10 +5436,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C190" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -5446,10 +5453,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C191" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -5463,10 +5470,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C192" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D192">
         <v>1</v>
@@ -5480,10 +5487,10 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C193" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D193">
         <v>1</v>
@@ -5497,10 +5504,10 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C194" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -5514,10 +5521,10 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C195" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D195">
         <v>1</v>
@@ -5531,10 +5538,10 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C196" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D196">
         <v>1</v>
@@ -5548,10 +5555,10 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C197" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D197">
         <v>1</v>
@@ -5565,10 +5572,10 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C198" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D198">
         <v>1</v>
@@ -5582,10 +5589,10 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C199" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D199">
         <v>1</v>
@@ -5599,10 +5606,10 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C200" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -5616,10 +5623,10 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C201" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -5633,10 +5640,10 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C202" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D202">
         <v>1</v>
@@ -5650,10 +5657,10 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C203" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -5667,10 +5674,10 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C204" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -5684,10 +5691,10 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C205" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -5701,10 +5708,10 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C206" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -5718,10 +5725,10 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C207" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D207">
         <v>1</v>
@@ -5735,10 +5742,10 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C208" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -5752,10 +5759,10 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C209" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D209">
         <v>1</v>
@@ -5769,10 +5776,10 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C210" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D210">
         <v>1</v>
@@ -5786,10 +5793,10 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C211" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -5803,10 +5810,10 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C212" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -5820,10 +5827,10 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C213" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D213">
         <v>1</v>
@@ -5837,10 +5844,10 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C214" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D214">
         <v>1</v>
@@ -5854,10 +5861,10 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C215" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D215">
         <v>1</v>
@@ -5871,10 +5878,10 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C216" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D216">
         <v>1</v>
@@ -5888,10 +5895,10 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C217" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -5905,10 +5912,10 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C218" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D218">
         <v>1</v>
@@ -5922,10 +5929,10 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C219" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D219">
         <v>1</v>
@@ -5939,10 +5946,10 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C220" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D220">
         <v>1</v>
@@ -5956,10 +5963,10 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C221" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D221">
         <v>1</v>
@@ -5973,10 +5980,10 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C222" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D222">
         <v>1</v>
@@ -5990,10 +5997,10 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C223" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D223">
         <v>1</v>
